--- a/DataSet/queue_data.xlsx
+++ b/DataSet/queue_data.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sandu\Documents\EEX5362\MP\Project\DataSet\DataSet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4BDA1DCA-9481-46A7-A467-079C36B971BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{916275F0-AD5F-4BD2-8BC2-07E0AEE84657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{E67BAB1F-4197-48C1-A4B7-C7F1A71A889D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{E67BAB1F-4197-48C1-A4B7-C7F1A71A889D}"/>
   </bookViews>
   <sheets>
-    <sheet name="queue_dataset" sheetId="1" r:id="rId1"/>
-    <sheet name="queue_data" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
+    <sheet name="queue_dataset" sheetId="1" r:id="rId2"/>
+    <sheet name="queue_data" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="229">
   <si>
     <t>arrival_time</t>
   </si>
@@ -727,12 +728,31 @@
   <si>
     <t>service_time</t>
   </si>
+  <si>
+    <t xml:space="preserve"> Arrival_Time</t>
+  </si>
+  <si>
+    <t>Service_Start_Time</t>
+  </si>
+  <si>
+    <t>Service_End_Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting_Time </t>
+  </si>
+  <si>
+    <t>Service_Time</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="h:mm:ss;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+  </numFmts>
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -866,6 +886,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1256,7 +1282,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
@@ -1278,6 +1304,9 @@
     <xf numFmtId="0" fontId="16" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1652,6 +1681,324 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822D9C2F-3F7C-468D-A1C8-7E1A68E4C306}">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.44140625" customWidth="1"/>
+    <col min="2" max="2" width="16.88671875" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" customWidth="1"/>
+    <col min="5" max="5" width="18.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="13">
+        <v>0.10668981481481482</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.10670138888888889</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.10805555555555556</v>
+      </c>
+      <c r="D2" s="12">
+        <f>C2-B2</f>
+        <v>1.3541666666666702E-3</v>
+      </c>
+      <c r="E2" s="12">
+        <f>B2 - A2</f>
+        <v>1.1574074074066631E-5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="13">
+        <v>0.10688657407407408</v>
+      </c>
+      <c r="B3" s="13">
+        <v>0.10805555555555556</v>
+      </c>
+      <c r="C3" s="13">
+        <v>0.10878472222222223</v>
+      </c>
+      <c r="D3" s="12">
+        <f t="shared" ref="D3:D16" si="0">C3-B3</f>
+        <v>7.2916666666666963E-4</v>
+      </c>
+      <c r="E3" s="12">
+        <f>B3 - A3</f>
+        <v>1.1689814814814792E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="13">
+        <v>0.10688657407407408</v>
+      </c>
+      <c r="B4" s="13">
+        <v>0.10878472222222223</v>
+      </c>
+      <c r="C4" s="13">
+        <v>0.10922453703703704</v>
+      </c>
+      <c r="D4" s="12">
+        <f t="shared" si="0"/>
+        <v>4.3981481481480955E-4</v>
+      </c>
+      <c r="E4" s="12">
+        <f t="shared" ref="E4:E16" si="1">B4 - A4</f>
+        <v>1.8981481481481488E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="13">
+        <v>0.10862268518518518</v>
+      </c>
+      <c r="B5" s="13">
+        <v>0.10922453703703704</v>
+      </c>
+      <c r="C5" s="13">
+        <v>0.10976851851851852</v>
+      </c>
+      <c r="D5" s="12">
+        <f t="shared" si="0"/>
+        <v>5.4398148148147862E-4</v>
+      </c>
+      <c r="E5" s="12">
+        <f t="shared" si="1"/>
+        <v>6.0185185185185341E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="13">
+        <v>0.10922453703703704</v>
+      </c>
+      <c r="B6" s="13">
+        <v>0.10976851851851852</v>
+      </c>
+      <c r="C6" s="13">
+        <v>0.11046296296296296</v>
+      </c>
+      <c r="D6" s="12">
+        <f t="shared" si="0"/>
+        <v>6.9444444444444198E-4</v>
+      </c>
+      <c r="E6" s="12">
+        <f t="shared" si="1"/>
+        <v>5.4398148148147862E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="13">
+        <v>0.11042824074074074</v>
+      </c>
+      <c r="B7" s="13">
+        <v>0.11046296296296296</v>
+      </c>
+      <c r="C7" s="13">
+        <v>0.11094907407407407</v>
+      </c>
+      <c r="D7" s="12">
+        <f t="shared" si="0"/>
+        <v>4.8611111111111771E-4</v>
+      </c>
+      <c r="E7" s="12">
+        <f t="shared" si="1"/>
+        <v>3.4722222222213772E-5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="13">
+        <v>0.1130324074074074</v>
+      </c>
+      <c r="B8" s="13">
+        <v>0.11357638888888889</v>
+      </c>
+      <c r="C8" s="13">
+        <v>0.11364583333333333</v>
+      </c>
+      <c r="D8" s="12">
+        <f t="shared" si="0"/>
+        <v>6.9444444444441422E-5</v>
+      </c>
+      <c r="E8" s="12">
+        <f t="shared" si="1"/>
+        <v>5.439814814814925E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
+        <v>0.11465277777777778</v>
+      </c>
+      <c r="B9" s="13">
+        <v>0.11546296296296296</v>
+      </c>
+      <c r="C9" s="13">
+        <v>0.11642361111111112</v>
+      </c>
+      <c r="D9" s="12">
+        <f t="shared" si="0"/>
+        <v>9.6064814814815491E-4</v>
+      </c>
+      <c r="E9" s="12">
+        <f t="shared" si="1"/>
+        <v>8.1018518518517768E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="13">
+        <v>0.11587962962962962</v>
+      </c>
+      <c r="B10" s="13">
+        <v>0.11642361111111112</v>
+      </c>
+      <c r="C10" s="13">
+        <v>0.11666666666666667</v>
+      </c>
+      <c r="D10" s="12">
+        <f t="shared" si="0"/>
+        <v>2.4305555555555192E-4</v>
+      </c>
+      <c r="E10" s="12">
+        <f t="shared" si="1"/>
+        <v>5.439814814814925E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
+        <v>0.11518518518518518</v>
+      </c>
+      <c r="B11" s="13">
+        <v>0.11642361111111112</v>
+      </c>
+      <c r="C11" s="13">
+        <v>0.11666666666666667</v>
+      </c>
+      <c r="D11" s="12">
+        <f t="shared" si="0"/>
+        <v>2.4305555555555192E-4</v>
+      </c>
+      <c r="E11" s="12">
+        <f t="shared" si="1"/>
+        <v>1.2384259259259345E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="13">
+        <v>0.1188425925925926</v>
+      </c>
+      <c r="B12" s="13">
+        <v>0.1188425925925926</v>
+      </c>
+      <c r="C12" s="13">
+        <v>0.11943287037037037</v>
+      </c>
+      <c r="D12" s="12">
+        <f t="shared" si="0"/>
+        <v>5.9027777777777291E-4</v>
+      </c>
+      <c r="E12" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
+        <v>0.1188425925925926</v>
+      </c>
+      <c r="B13" s="13">
+        <v>0.11943287037037037</v>
+      </c>
+      <c r="C13" s="13">
+        <v>0.12180555555555556</v>
+      </c>
+      <c r="D13" s="12">
+        <f t="shared" si="0"/>
+        <v>2.372685185185186E-3</v>
+      </c>
+      <c r="E13" s="12">
+        <f t="shared" si="1"/>
+        <v>5.9027777777777291E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="13">
+        <v>0.12023148148148148</v>
+      </c>
+      <c r="B14" s="13">
+        <v>0.12180555555555556</v>
+      </c>
+      <c r="C14" s="13">
+        <v>0.12262731481481481</v>
+      </c>
+      <c r="D14" s="12">
+        <f t="shared" si="0"/>
+        <v>8.2175925925925819E-4</v>
+      </c>
+      <c r="E14" s="12">
+        <f t="shared" si="1"/>
+        <v>1.574074074074075E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
+        <v>0.12290509259259259</v>
+      </c>
+      <c r="B15" s="13">
+        <v>0.12290509259259259</v>
+      </c>
+      <c r="C15" s="13">
+        <v>0.12314814814814815</v>
+      </c>
+      <c r="D15" s="12">
+        <f t="shared" si="0"/>
+        <v>2.4305555555555192E-4</v>
+      </c>
+      <c r="E15" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="13">
+        <v>0.12332175925925926</v>
+      </c>
+      <c r="B16" s="13">
+        <v>0.12387731481481482</v>
+      </c>
+      <c r="C16" s="13">
+        <v>0.1252662037037037</v>
+      </c>
+      <c r="D16" s="12">
+        <f t="shared" si="0"/>
+        <v>1.388888888888884E-3</v>
+      </c>
+      <c r="E16" s="12">
+        <f t="shared" si="1"/>
+        <v>5.5555555555555913E-4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1683381-3DE1-4C2E-AE43-C19BDEA15690}">
   <dimension ref="A1:E561"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11205,7 +11552,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED6CF3A-154D-4521-B86A-C5AF96E2449B}">
   <dimension ref="A1:P23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11547,23 +11894,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="6a0bfadc-bd5e-44df-b90d-7cd381f3fed0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007B339CB11AB16C4E93D2BB0BC14C00C1" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1f6aec53bd09902fc21ff78453954f78">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="6a0bfadc-bd5e-44df-b90d-7cd381f3fed0" xmlns:ns4="83dcc381-1f31-4cb6-af5a-2a9c5f62a0fa" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="81a2c0f5029bedb18df5c0ef8e7df6a6" ns3:_="" ns4:_="">
     <xsd:import namespace="6a0bfadc-bd5e-44df-b90d-7cd381f3fed0"/>
@@ -11810,32 +12140,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A27FB7E-8BC7-4B65-9DAB-0C079A24E7FA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="83dcc381-1f31-4cb6-af5a-2a9c5f62a0fa"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="6a0bfadc-bd5e-44df-b90d-7cd381f3fed0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F09FE76-7BDD-4C52-B0EA-8B91744AA160}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="6a0bfadc-bd5e-44df-b90d-7cd381f3fed0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF6766EE-8447-4704-AAE1-3EB49C133538}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11852,4 +12174,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F09FE76-7BDD-4C52-B0EA-8B91744AA160}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A27FB7E-8BC7-4B65-9DAB-0C079A24E7FA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="83dcc381-1f31-4cb6-af5a-2a9c5f62a0fa"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="6a0bfadc-bd5e-44df-b90d-7cd381f3fed0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>